--- a/example/sample.xlsx
+++ b/example/sample.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\ayebee\source\repos\Resumaker\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE71C7A0-A10A-4B94-ACE1-C52516B5BCC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED04647F-934D-4FDD-8EB2-2D4FA4085662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-150" yWindow="-150" windowWidth="38700" windowHeight="21180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,8 +16,8 @@
     <sheet name="履歴書" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="Excel_BuiltIn_Print_Area" localSheetId="0">履歴書!$A$1:$I$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">履歴書!$A$1:$N$39</definedName>
+    <definedName name="Excel_BuiltIn_Print_Area" localSheetId="0">履歴書!$B$2:$J$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">履歴書!$A$1:$O$40</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1263,6 +1263,12 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1460,12 +1466,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1490,15 +1490,15 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
+      <xdr:col>8</xdr:col>
       <xdr:colOff>157275</xdr:colOff>
-      <xdr:row>0</xdr:row>
+      <xdr:row>1</xdr:row>
       <xdr:rowOff>114450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
+      <xdr:col>10</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>7</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -1755,791 +1755,793 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N39"/>
+  <dimension ref="B1:O40"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="10.140625" customWidth="1"/>
-    <col min="2" max="2" width="4.85546875" customWidth="1"/>
-    <col min="3" max="3" width="21.28515625" customWidth="1"/>
-    <col min="4" max="4" width="32.42578125" customWidth="1"/>
-    <col min="5" max="5" width="6.85546875" customWidth="1"/>
-    <col min="6" max="6" width="2.5703125" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" customWidth="1"/>
-    <col min="8" max="8" width="10.140625" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" customWidth="1"/>
-    <col min="10" max="11" width="3.28515625" customWidth="1"/>
-    <col min="12" max="12" width="75.42578125" customWidth="1"/>
-    <col min="13" max="13" width="1.140625" customWidth="1"/>
-    <col min="14" max="14" width="19.85546875" customWidth="1"/>
-    <col min="15" max="19" width="7.5703125" customWidth="1"/>
+    <col min="1" max="1" width="0.42578125" customWidth="1"/>
+    <col min="2" max="2" width="10.140625" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" customWidth="1"/>
+    <col min="4" max="4" width="21.28515625" customWidth="1"/>
+    <col min="5" max="5" width="32.42578125" customWidth="1"/>
+    <col min="6" max="6" width="6.85546875" customWidth="1"/>
+    <col min="7" max="7" width="2.5703125" customWidth="1"/>
+    <col min="8" max="8" width="5.7109375" customWidth="1"/>
+    <col min="9" max="9" width="10.140625" customWidth="1"/>
+    <col min="10" max="10" width="5.7109375" customWidth="1"/>
+    <col min="11" max="12" width="3.28515625" customWidth="1"/>
+    <col min="13" max="13" width="75.42578125" customWidth="1"/>
+    <col min="14" max="14" width="1.140625" customWidth="1"/>
+    <col min="15" max="15" width="19.85546875" customWidth="1"/>
+    <col min="16" max="20" width="7.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="30" customHeight="1">
-      <c r="A1" s="99" t="s">
+    <row r="1" spans="2:15" ht="3.75" customHeight="1"/>
+    <row r="2" spans="2:15" ht="30" customHeight="1">
+      <c r="B2" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="99"/>
-      <c r="C1" s="99"/>
-      <c r="D1" s="58" t="s">
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="60" t="s">
         <v>23</v>
       </c>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="59"/>
-      <c r="H1" s="2"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-    </row>
-    <row r="2" spans="1:14" ht="7.5" customHeight="1">
-      <c r="A2" s="100"/>
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-    </row>
-    <row r="3" spans="1:14" ht="17.25" customHeight="1">
-      <c r="A3" s="11" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" s="48" t="s">
-        <v>21</v>
-      </c>
+      <c r="F2" s="61"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="2"/>
+      <c r="M2" s="1"/>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
+    </row>
+    <row r="3" spans="2:15" ht="7.5" customHeight="1">
+      <c r="B3" s="34"/>
       <c r="C3" s="34"/>
       <c r="D3" s="34"/>
-      <c r="E3" s="60" t="s">
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+    </row>
+    <row r="4" spans="2:15" ht="17.25" customHeight="1">
+      <c r="B4" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="50" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="36"/>
+      <c r="E4" s="36"/>
+      <c r="F4" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="61"/>
-      <c r="G3" s="61"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="13"/>
-      <c r="L3" s="62" t="s">
+      <c r="G4" s="63"/>
+      <c r="H4" s="63"/>
+      <c r="I4" s="12"/>
+      <c r="J4" s="13"/>
+      <c r="M4" s="64" t="s">
         <v>19</v>
       </c>
-      <c r="M3" s="61"/>
-      <c r="N3" s="63"/>
-    </row>
-    <row r="4" spans="1:14" ht="7.5" customHeight="1">
-      <c r="A4" s="39" t="s">
+      <c r="N4" s="63"/>
+      <c r="O4" s="65"/>
+    </row>
+    <row r="5" spans="2:15" ht="7.5" customHeight="1">
+      <c r="B5" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="C5" s="47" t="s">
         <v>20</v>
       </c>
-      <c r="C4" s="46"/>
-      <c r="D4" s="46"/>
-      <c r="E4" s="86" t="s">
+      <c r="D5" s="48"/>
+      <c r="E5" s="48"/>
+      <c r="F5" s="88" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="I4" s="14"/>
-      <c r="L4" s="64"/>
-      <c r="M4" s="65"/>
-      <c r="N4" s="66"/>
-    </row>
-    <row r="5" spans="1:14" ht="16.5" customHeight="1">
-      <c r="A5" s="40"/>
-      <c r="B5" s="46"/>
-      <c r="C5" s="46"/>
-      <c r="D5" s="46"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="46"/>
-      <c r="I5" s="14"/>
-      <c r="L5" s="69" t="s">
+      <c r="G5" s="48"/>
+      <c r="H5" s="48"/>
+      <c r="J5" s="14"/>
+      <c r="M5" s="66"/>
+      <c r="N5" s="67"/>
+      <c r="O5" s="68"/>
+    </row>
+    <row r="6" spans="2:15" ht="16.5" customHeight="1">
+      <c r="B6" s="42"/>
+      <c r="C6" s="48"/>
+      <c r="D6" s="48"/>
+      <c r="E6" s="48"/>
+      <c r="F6" s="89"/>
+      <c r="G6" s="48"/>
+      <c r="H6" s="48"/>
+      <c r="J6" s="14"/>
+      <c r="M6" s="71" t="s">
         <v>78</v>
       </c>
-      <c r="M5" s="70"/>
-      <c r="N5" s="71"/>
-    </row>
-    <row r="6" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A6" s="41"/>
-      <c r="B6" s="47"/>
-      <c r="C6" s="47"/>
-      <c r="D6" s="47"/>
-      <c r="E6" s="88"/>
-      <c r="F6" s="47"/>
-      <c r="G6" s="47"/>
-      <c r="H6" s="15"/>
-      <c r="I6" s="16"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="46"/>
       <c r="N6" s="72"/>
-    </row>
-    <row r="7" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A7" s="19" t="s">
+      <c r="O6" s="73"/>
+    </row>
+    <row r="7" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B7" s="43"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="90"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="16"/>
+      <c r="M7" s="42"/>
+      <c r="N7" s="48"/>
+      <c r="O7" s="74"/>
+    </row>
+    <row r="8" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B8" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B7" s="92" t="s">
+      <c r="C8" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="92"/>
-      <c r="D7" s="93"/>
-      <c r="E7" s="36" t="s">
+      <c r="D8" s="94"/>
+      <c r="E8" s="95"/>
+      <c r="F8" s="38" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="38"/>
-      <c r="L7" s="40"/>
-      <c r="M7" s="46"/>
-      <c r="N7" s="72"/>
-    </row>
-    <row r="8" spans="1:14" ht="17.25" customHeight="1">
-      <c r="A8" s="11" t="s">
+      <c r="G8" s="39"/>
+      <c r="H8" s="39"/>
+      <c r="I8" s="39"/>
+      <c r="J8" s="40"/>
+      <c r="M8" s="42"/>
+      <c r="N8" s="48"/>
+      <c r="O8" s="74"/>
+    </row>
+    <row r="9" spans="2:15" ht="17.25" customHeight="1">
+      <c r="B9" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="48" t="s">
+      <c r="C9" s="50" t="s">
         <v>25</v>
       </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="62" t="s">
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="64" t="s">
         <v>5</v>
       </c>
-      <c r="F8" s="89"/>
-      <c r="G8" s="89"/>
-      <c r="H8" s="89"/>
-      <c r="I8" s="90"/>
-      <c r="L8" s="40"/>
-      <c r="M8" s="46"/>
-      <c r="N8" s="72"/>
-    </row>
-    <row r="9" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A9" s="29" t="s">
+      <c r="G9" s="91"/>
+      <c r="H9" s="91"/>
+      <c r="I9" s="91"/>
+      <c r="J9" s="92"/>
+      <c r="M9" s="42"/>
+      <c r="N9" s="48"/>
+      <c r="O9" s="74"/>
+    </row>
+    <row r="10" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B10" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="42" t="s">
+      <c r="C10" s="44" t="s">
         <v>26</v>
       </c>
-      <c r="C9" s="43"/>
-      <c r="D9" s="44"/>
-      <c r="E9" s="28" t="s">
+      <c r="D10" s="45"/>
+      <c r="E10" s="46"/>
+      <c r="F10" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="91" t="s">
+      <c r="G10" s="93" t="s">
         <v>85</v>
       </c>
-      <c r="G9" s="46"/>
-      <c r="H9" s="46"/>
-      <c r="I9" s="72"/>
-      <c r="L9" s="40"/>
-      <c r="M9" s="46"/>
-      <c r="N9" s="72"/>
-    </row>
-    <row r="10" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A10" s="17" t="s">
+      <c r="H10" s="48"/>
+      <c r="I10" s="48"/>
+      <c r="J10" s="74"/>
+      <c r="M10" s="42"/>
+      <c r="N10" s="48"/>
+      <c r="O10" s="74"/>
+    </row>
+    <row r="11" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B11" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="52" t="s">
+      <c r="C11" s="54" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="47"/>
-      <c r="D10" s="47"/>
-      <c r="E10" s="30" t="s">
+      <c r="D11" s="49"/>
+      <c r="E11" s="49"/>
+      <c r="F11" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="49" t="s">
+      <c r="G11" s="51" t="s">
         <v>84</v>
       </c>
-      <c r="G10" s="50"/>
-      <c r="H10" s="50"/>
-      <c r="I10" s="51"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="46"/>
-      <c r="N10" s="72"/>
-    </row>
-    <row r="11" spans="1:14" ht="7.5" customHeight="1">
-      <c r="A11" s="5"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="6"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="46"/>
-      <c r="N11" s="72"/>
-    </row>
-    <row r="12" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A12" s="20" t="s">
+      <c r="H11" s="52"/>
+      <c r="I11" s="52"/>
+      <c r="J11" s="53"/>
+      <c r="M11" s="42"/>
+      <c r="N11" s="48"/>
+      <c r="O11" s="74"/>
+    </row>
+    <row r="12" spans="2:15" ht="7.5" customHeight="1">
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="6"/>
+      <c r="M12" s="42"/>
+      <c r="N12" s="48"/>
+      <c r="O12" s="74"/>
+    </row>
+    <row r="13" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B13" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="C13" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="36" t="s">
+      <c r="D13" s="38" t="s">
         <v>10</v>
       </c>
-      <c r="D12" s="53"/>
-      <c r="E12" s="53"/>
-      <c r="F12" s="53"/>
-      <c r="G12" s="53"/>
-      <c r="H12" s="53"/>
-      <c r="I12" s="54"/>
-      <c r="L12" s="40"/>
-      <c r="M12" s="46"/>
-      <c r="N12" s="72"/>
-    </row>
-    <row r="13" spans="1:14" ht="7.5" customHeight="1">
-      <c r="L13" s="40"/>
-      <c r="M13" s="46"/>
-      <c r="N13" s="72"/>
-    </row>
-    <row r="14" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A14" s="33" t="s">
+      <c r="E13" s="55"/>
+      <c r="F13" s="55"/>
+      <c r="G13" s="55"/>
+      <c r="H13" s="55"/>
+      <c r="I13" s="55"/>
+      <c r="J13" s="56"/>
+      <c r="M13" s="42"/>
+      <c r="N13" s="48"/>
+      <c r="O13" s="74"/>
+    </row>
+    <row r="14" spans="2:15" ht="7.5" customHeight="1">
+      <c r="M14" s="42"/>
+      <c r="N14" s="48"/>
+      <c r="O14" s="74"/>
+    </row>
+    <row r="15" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B15" s="35" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
-      <c r="I14" s="35"/>
-      <c r="L14" s="40"/>
-      <c r="M14" s="46"/>
-      <c r="N14" s="72"/>
-    </row>
-    <row r="15" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A15" s="22" t="s">
+      <c r="C15" s="36"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" s="37"/>
+      <c r="M15" s="42"/>
+      <c r="N15" s="48"/>
+      <c r="O15" s="74"/>
+    </row>
+    <row r="16" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B16" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="C16" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="55" t="s">
+      <c r="D16" s="57" t="s">
         <v>33</v>
       </c>
-      <c r="D15" s="56"/>
-      <c r="E15" s="56"/>
-      <c r="F15" s="56"/>
-      <c r="G15" s="56"/>
-      <c r="H15" s="56"/>
-      <c r="I15" s="57"/>
-      <c r="L15" s="40"/>
-      <c r="M15" s="46"/>
-      <c r="N15" s="72"/>
-    </row>
-    <row r="16" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A16" s="22" t="s">
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="59"/>
+      <c r="M16" s="42"/>
+      <c r="N16" s="48"/>
+      <c r="O16" s="74"/>
+    </row>
+    <row r="17" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B17" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="7" t="s">
+      <c r="C17" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="55" t="s">
+      <c r="D17" s="57" t="s">
         <v>38</v>
       </c>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
-      <c r="I16" s="57"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="46"/>
-      <c r="N16" s="72"/>
-    </row>
-    <row r="17" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A17" s="22" t="s">
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="59"/>
+      <c r="M17" s="42"/>
+      <c r="N17" s="48"/>
+      <c r="O17" s="74"/>
+    </row>
+    <row r="18" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B18" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="7" t="s">
+      <c r="C18" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C17" s="55" t="s">
+      <c r="D18" s="57" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="56"/>
-      <c r="E17" s="56"/>
-      <c r="F17" s="56"/>
-      <c r="G17" s="56"/>
-      <c r="H17" s="56"/>
-      <c r="I17" s="57"/>
-      <c r="L17" s="40"/>
-      <c r="M17" s="46"/>
-      <c r="N17" s="72"/>
-    </row>
-    <row r="18" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A18" s="23" t="s">
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="59"/>
+      <c r="M18" s="42"/>
+      <c r="N18" s="48"/>
+      <c r="O18" s="74"/>
+    </row>
+    <row r="19" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B19" s="23" t="s">
         <v>35</v>
       </c>
-      <c r="B18" s="24" t="s">
+      <c r="C19" s="24" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="82" t="s">
+      <c r="D19" s="84" t="s">
         <v>40</v>
       </c>
-      <c r="D18" s="83"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="83"/>
-      <c r="G18" s="83"/>
-      <c r="H18" s="83"/>
-      <c r="I18" s="84"/>
-      <c r="L18" s="40"/>
-      <c r="M18" s="46"/>
-      <c r="N18" s="72"/>
-    </row>
-    <row r="19" spans="1:14" ht="7.5" customHeight="1">
-      <c r="A19" s="3"/>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="G19" s="3"/>
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-      <c r="J19" s="3"/>
-      <c r="K19" s="3"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="46"/>
-      <c r="N19" s="72"/>
-    </row>
-    <row r="20" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A20" s="33" t="s">
+      <c r="E19" s="85"/>
+      <c r="F19" s="85"/>
+      <c r="G19" s="85"/>
+      <c r="H19" s="85"/>
+      <c r="I19" s="85"/>
+      <c r="J19" s="86"/>
+      <c r="M19" s="42"/>
+      <c r="N19" s="48"/>
+      <c r="O19" s="74"/>
+    </row>
+    <row r="20" spans="2:15" ht="7.5" customHeight="1">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+      <c r="D20" s="3"/>
+      <c r="E20" s="3"/>
+      <c r="F20" s="3"/>
+      <c r="G20" s="3"/>
+      <c r="H20" s="3"/>
+      <c r="I20" s="3"/>
+      <c r="J20" s="3"/>
+      <c r="K20" s="3"/>
+      <c r="L20" s="3"/>
+      <c r="M20" s="42"/>
+      <c r="N20" s="48"/>
+      <c r="O20" s="74"/>
+    </row>
+    <row r="21" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B21" s="35" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="34"/>
-      <c r="C20" s="34"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="35"/>
-      <c r="L20" s="40"/>
-      <c r="M20" s="46"/>
-      <c r="N20" s="72"/>
-    </row>
-    <row r="21" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A21" s="22" t="s">
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="37"/>
+      <c r="M21" s="42"/>
+      <c r="N21" s="48"/>
+      <c r="O21" s="74"/>
+    </row>
+    <row r="22" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B22" s="22" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="C22" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C21" s="55" t="s">
+      <c r="D22" s="57" t="s">
         <v>43</v>
       </c>
-      <c r="D21" s="56"/>
-      <c r="E21" s="56"/>
-      <c r="F21" s="56"/>
-      <c r="G21" s="56"/>
-      <c r="H21" s="56"/>
-      <c r="I21" s="57"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="72"/>
-    </row>
-    <row r="22" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A22" s="22" t="s">
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="59"/>
+      <c r="M22" s="42"/>
+      <c r="N22" s="48"/>
+      <c r="O22" s="74"/>
+    </row>
+    <row r="23" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B23" s="22" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="7" t="s">
+      <c r="C23" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C22" s="55" t="s">
+      <c r="D23" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="D22" s="56"/>
-      <c r="E22" s="56"/>
-      <c r="F22" s="56"/>
-      <c r="G22" s="56"/>
-      <c r="H22" s="56"/>
-      <c r="I22" s="57"/>
-      <c r="L22" s="40"/>
-      <c r="M22" s="46"/>
-      <c r="N22" s="72"/>
-    </row>
-    <row r="23" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A23" s="22" t="s">
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="59"/>
+      <c r="M23" s="42"/>
+      <c r="N23" s="48"/>
+      <c r="O23" s="74"/>
+    </row>
+    <row r="24" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B24" s="22" t="s">
         <v>45</v>
       </c>
-      <c r="B23" s="7" t="s">
+      <c r="C24" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="C23" s="55" t="s">
+      <c r="D24" s="57" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="56"/>
-      <c r="E23" s="56"/>
-      <c r="F23" s="56"/>
-      <c r="G23" s="56"/>
-      <c r="H23" s="56"/>
-      <c r="I23" s="57"/>
-      <c r="L23" s="73"/>
-      <c r="M23" s="50"/>
-      <c r="N23" s="51"/>
-    </row>
-    <row r="24" spans="1:14" ht="7.5" customHeight="1">
-      <c r="A24" s="67" t="s">
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="59"/>
+      <c r="M24" s="75"/>
+      <c r="N24" s="52"/>
+      <c r="O24" s="53"/>
+    </row>
+    <row r="25" spans="2:15" ht="7.5" customHeight="1">
+      <c r="B25" s="69" t="s">
         <v>50</v>
       </c>
-      <c r="B24" s="74" t="s">
+      <c r="C25" s="76" t="s">
         <v>51</v>
       </c>
-      <c r="C24" s="76" t="s">
+      <c r="D25" s="78" t="s">
         <v>52</v>
       </c>
-      <c r="D24" s="77"/>
-      <c r="E24" s="77"/>
-      <c r="F24" s="77"/>
-      <c r="G24" s="77"/>
-      <c r="H24" s="77"/>
-      <c r="I24" s="78"/>
-      <c r="J24" s="3"/>
-      <c r="K24" s="3"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="8"/>
-      <c r="N24" s="8"/>
-    </row>
-    <row r="25" spans="1:14" ht="17.25" customHeight="1">
-      <c r="A25" s="68"/>
-      <c r="B25" s="75"/>
-      <c r="C25" s="79"/>
-      <c r="D25" s="80"/>
-      <c r="E25" s="80"/>
-      <c r="F25" s="80"/>
-      <c r="G25" s="80"/>
-      <c r="H25" s="80"/>
-      <c r="I25" s="81"/>
-      <c r="L25" s="62" t="s">
+      <c r="E25" s="79"/>
+      <c r="F25" s="79"/>
+      <c r="G25" s="79"/>
+      <c r="H25" s="79"/>
+      <c r="I25" s="79"/>
+      <c r="J25" s="80"/>
+      <c r="K25" s="3"/>
+      <c r="L25" s="3"/>
+      <c r="M25" s="8"/>
+      <c r="N25" s="8"/>
+      <c r="O25" s="8"/>
+    </row>
+    <row r="26" spans="2:15" ht="17.25" customHeight="1">
+      <c r="B26" s="70"/>
+      <c r="C26" s="77"/>
+      <c r="D26" s="81"/>
+      <c r="E26" s="82"/>
+      <c r="F26" s="82"/>
+      <c r="G26" s="82"/>
+      <c r="H26" s="82"/>
+      <c r="I26" s="82"/>
+      <c r="J26" s="83"/>
+      <c r="M26" s="64" t="s">
         <v>82</v>
       </c>
-      <c r="M25" s="61"/>
-      <c r="N25" s="63"/>
-    </row>
-    <row r="26" spans="1:14" ht="7.5" customHeight="1">
-      <c r="A26" s="67" t="s">
+      <c r="N26" s="63"/>
+      <c r="O26" s="65"/>
+    </row>
+    <row r="27" spans="2:15" ht="7.5" customHeight="1">
+      <c r="B27" s="69" t="s">
         <v>53</v>
       </c>
-      <c r="B26" s="74" t="s">
+      <c r="C27" s="76" t="s">
         <v>54</v>
       </c>
-      <c r="C26" s="76" t="s">
+      <c r="D27" s="78" t="s">
         <v>55</v>
       </c>
-      <c r="D26" s="77"/>
-      <c r="E26" s="77"/>
-      <c r="F26" s="77"/>
-      <c r="G26" s="77"/>
-      <c r="H26" s="77"/>
-      <c r="I26" s="78"/>
-      <c r="L26" s="64"/>
-      <c r="M26" s="65"/>
-      <c r="N26" s="66"/>
-    </row>
-    <row r="27" spans="1:14" ht="17.25" customHeight="1">
-      <c r="A27" s="68"/>
-      <c r="B27" s="75"/>
-      <c r="C27" s="79"/>
-      <c r="D27" s="80"/>
-      <c r="E27" s="80"/>
-      <c r="F27" s="80"/>
-      <c r="G27" s="80"/>
-      <c r="H27" s="80"/>
-      <c r="I27" s="81"/>
-      <c r="L27" s="69" t="s">
+      <c r="E27" s="79"/>
+      <c r="F27" s="79"/>
+      <c r="G27" s="79"/>
+      <c r="H27" s="79"/>
+      <c r="I27" s="79"/>
+      <c r="J27" s="80"/>
+      <c r="M27" s="66"/>
+      <c r="N27" s="67"/>
+      <c r="O27" s="68"/>
+    </row>
+    <row r="28" spans="2:15" ht="17.25" customHeight="1">
+      <c r="B28" s="70"/>
+      <c r="C28" s="77"/>
+      <c r="D28" s="81"/>
+      <c r="E28" s="82"/>
+      <c r="F28" s="82"/>
+      <c r="G28" s="82"/>
+      <c r="H28" s="82"/>
+      <c r="I28" s="82"/>
+      <c r="J28" s="83"/>
+      <c r="M28" s="71" t="s">
         <v>83</v>
       </c>
-      <c r="M27" s="70"/>
-      <c r="N27" s="71"/>
-    </row>
-    <row r="28" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A28" s="22" t="s">
+      <c r="N28" s="72"/>
+      <c r="O28" s="73"/>
+    </row>
+    <row r="29" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B29" s="22" t="s">
         <v>56</v>
       </c>
-      <c r="B28" s="7" t="s">
+      <c r="C29" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="C28" s="55" t="s">
+      <c r="D29" s="57" t="s">
         <v>58</v>
       </c>
-      <c r="D28" s="56"/>
-      <c r="E28" s="56"/>
-      <c r="F28" s="56"/>
-      <c r="G28" s="56"/>
-      <c r="H28" s="56"/>
-      <c r="I28" s="57"/>
-      <c r="L28" s="40"/>
-      <c r="M28" s="46"/>
-      <c r="N28" s="72"/>
-    </row>
-    <row r="29" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A29" s="22" t="s">
+      <c r="E29" s="58"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="58"/>
+      <c r="J29" s="59"/>
+      <c r="M29" s="42"/>
+      <c r="N29" s="48"/>
+      <c r="O29" s="74"/>
+    </row>
+    <row r="30" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B30" s="22" t="s">
         <v>59</v>
       </c>
-      <c r="B29" s="7" t="s">
+      <c r="C30" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="C29" s="55" t="s">
+      <c r="D30" s="57" t="s">
         <v>65</v>
       </c>
-      <c r="D29" s="56"/>
-      <c r="E29" s="56"/>
-      <c r="F29" s="56"/>
-      <c r="G29" s="56"/>
-      <c r="H29" s="56"/>
-      <c r="I29" s="57"/>
-      <c r="L29" s="40"/>
-      <c r="M29" s="46"/>
-      <c r="N29" s="72"/>
-    </row>
-    <row r="30" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A30" s="22" t="s">
+      <c r="E30" s="58"/>
+      <c r="F30" s="58"/>
+      <c r="G30" s="58"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="58"/>
+      <c r="J30" s="59"/>
+      <c r="M30" s="42"/>
+      <c r="N30" s="48"/>
+      <c r="O30" s="74"/>
+    </row>
+    <row r="31" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B31" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="B30" s="7" t="s">
+      <c r="C31" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C30" s="55" t="s">
+      <c r="D31" s="57" t="s">
         <v>66</v>
       </c>
-      <c r="D30" s="56"/>
-      <c r="E30" s="56"/>
-      <c r="F30" s="56"/>
-      <c r="G30" s="56"/>
-      <c r="H30" s="56"/>
-      <c r="I30" s="57"/>
-      <c r="L30" s="40"/>
-      <c r="M30" s="46"/>
-      <c r="N30" s="72"/>
-    </row>
-    <row r="31" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A31" s="23" t="s">
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="59"/>
+      <c r="M31" s="42"/>
+      <c r="N31" s="48"/>
+      <c r="O31" s="74"/>
+    </row>
+    <row r="32" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B32" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="C32" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="82" t="s">
+      <c r="D32" s="84" t="s">
         <v>67</v>
       </c>
-      <c r="D31" s="83"/>
-      <c r="E31" s="83"/>
-      <c r="F31" s="83"/>
-      <c r="G31" s="83"/>
-      <c r="H31" s="83"/>
-      <c r="I31" s="84"/>
-      <c r="L31" s="73"/>
-      <c r="M31" s="50"/>
-      <c r="N31" s="51"/>
-    </row>
-    <row r="32" spans="1:14" ht="7.5" customHeight="1">
-      <c r="A32" s="18"/>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
-    </row>
-    <row r="33" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A33" s="33" t="s">
+      <c r="E32" s="85"/>
+      <c r="F32" s="85"/>
+      <c r="G32" s="85"/>
+      <c r="H32" s="85"/>
+      <c r="I32" s="85"/>
+      <c r="J32" s="86"/>
+      <c r="M32" s="75"/>
+      <c r="N32" s="52"/>
+      <c r="O32" s="53"/>
+    </row>
+    <row r="33" spans="2:15" ht="7.5" customHeight="1">
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
+      <c r="J33" s="18"/>
+    </row>
+    <row r="34" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B34" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="B33" s="34"/>
-      <c r="C33" s="34"/>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="35"/>
-      <c r="L33" s="33" t="s">
+      <c r="C34" s="36"/>
+      <c r="D34" s="36"/>
+      <c r="E34" s="36"/>
+      <c r="F34" s="36"/>
+      <c r="G34" s="36"/>
+      <c r="H34" s="36"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="37"/>
+      <c r="M34" s="35" t="s">
         <v>13</v>
       </c>
-      <c r="M33" s="34"/>
-      <c r="N33" s="35"/>
-    </row>
-    <row r="34" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A34" s="22" t="s">
+      <c r="N34" s="36"/>
+      <c r="O34" s="37"/>
+    </row>
+    <row r="35" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B35" s="22" t="s">
         <v>68</v>
       </c>
-      <c r="B34" s="7" t="s">
+      <c r="C35" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C34" s="55" t="s">
+      <c r="D35" s="57" t="s">
         <v>69</v>
       </c>
-      <c r="D34" s="56"/>
-      <c r="E34" s="56"/>
-      <c r="F34" s="56"/>
-      <c r="G34" s="56"/>
-      <c r="H34" s="56"/>
-      <c r="I34" s="57"/>
-      <c r="L34" s="85" t="s">
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="59"/>
+      <c r="M35" s="87" t="s">
         <v>79</v>
       </c>
-      <c r="M34" s="70"/>
-      <c r="N34" s="71"/>
-    </row>
-    <row r="35" spans="1:14" ht="17.25" customHeight="1">
-      <c r="A35" s="67" t="s">
+      <c r="N35" s="72"/>
+      <c r="O35" s="73"/>
+    </row>
+    <row r="36" spans="2:15" ht="17.25" customHeight="1">
+      <c r="B36" s="69" t="s">
         <v>70</v>
       </c>
-      <c r="B35" s="74" t="s">
+      <c r="C36" s="76" t="s">
         <v>87</v>
       </c>
-      <c r="C35" s="76" t="s">
+      <c r="D36" s="78" t="s">
         <v>71</v>
       </c>
-      <c r="D35" s="77"/>
-      <c r="E35" s="77"/>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
-      <c r="I35" s="78"/>
-      <c r="L35" s="73"/>
-      <c r="M35" s="50"/>
-      <c r="N35" s="51"/>
-    </row>
-    <row r="36" spans="1:14" ht="7.5" customHeight="1">
-      <c r="A36" s="68"/>
-      <c r="B36" s="75"/>
-      <c r="C36" s="79"/>
-      <c r="D36" s="80"/>
-      <c r="E36" s="80"/>
-      <c r="F36" s="80"/>
-      <c r="G36" s="80"/>
-      <c r="H36" s="80"/>
-      <c r="I36" s="81"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="10"/>
-    </row>
-    <row r="37" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A37" s="26" t="s">
+      <c r="E36" s="79"/>
+      <c r="F36" s="79"/>
+      <c r="G36" s="79"/>
+      <c r="H36" s="79"/>
+      <c r="I36" s="79"/>
+      <c r="J36" s="80"/>
+      <c r="M36" s="75"/>
+      <c r="N36" s="52"/>
+      <c r="O36" s="53"/>
+    </row>
+    <row r="37" spans="2:15" ht="7.5" customHeight="1">
+      <c r="B37" s="70"/>
+      <c r="C37" s="77"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="82"/>
+      <c r="F37" s="82"/>
+      <c r="G37" s="82"/>
+      <c r="H37" s="82"/>
+      <c r="I37" s="82"/>
+      <c r="J37" s="83"/>
+      <c r="M37" s="9"/>
+      <c r="N37" s="9"/>
+      <c r="O37" s="10"/>
+    </row>
+    <row r="38" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B38" s="26" t="s">
         <v>72</v>
       </c>
-      <c r="B37" s="27" t="s">
+      <c r="C38" s="27" t="s">
         <v>88</v>
       </c>
-      <c r="C37" s="79" t="s">
+      <c r="D38" s="81" t="s">
         <v>73</v>
       </c>
-      <c r="D37" s="65"/>
-      <c r="E37" s="65"/>
-      <c r="F37" s="65"/>
-      <c r="G37" s="65"/>
-      <c r="H37" s="65"/>
-      <c r="I37" s="66"/>
-      <c r="L37" s="25" t="s">
+      <c r="E38" s="67"/>
+      <c r="F38" s="67"/>
+      <c r="G38" s="67"/>
+      <c r="H38" s="67"/>
+      <c r="I38" s="67"/>
+      <c r="J38" s="68"/>
+      <c r="M38" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="M37" s="4"/>
-      <c r="N37" s="25" t="s">
+      <c r="N38" s="4"/>
+      <c r="O38" s="25" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="38" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A38" s="26" t="s">
+    <row r="39" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B39" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="B38" s="27" t="s">
+      <c r="C39" s="27" t="s">
         <v>89</v>
       </c>
-      <c r="C38" s="79" t="s">
+      <c r="D39" s="81" t="s">
         <v>76</v>
       </c>
-      <c r="D38" s="65"/>
-      <c r="E38" s="65"/>
-      <c r="F38" s="65"/>
-      <c r="G38" s="65"/>
-      <c r="H38" s="65"/>
-      <c r="I38" s="66"/>
-      <c r="L38" s="94" t="s">
+      <c r="E39" s="67"/>
+      <c r="F39" s="67"/>
+      <c r="G39" s="67"/>
+      <c r="H39" s="67"/>
+      <c r="I39" s="67"/>
+      <c r="J39" s="68"/>
+      <c r="M39" s="96" t="s">
         <v>80</v>
       </c>
-      <c r="M38" s="9"/>
-      <c r="N38" s="96" t="s">
+      <c r="N39" s="9"/>
+      <c r="O39" s="98" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="39" spans="1:14" ht="24.75" customHeight="1">
-      <c r="A39" s="31" t="s">
+    <row r="40" spans="2:15" ht="24.75" customHeight="1">
+      <c r="B40" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="C40" s="32" t="s">
         <v>90</v>
       </c>
-      <c r="C39" s="97" t="s">
+      <c r="D40" s="99" t="s">
         <v>77</v>
       </c>
-      <c r="D39" s="47"/>
-      <c r="E39" s="47"/>
-      <c r="F39" s="47"/>
-      <c r="G39" s="47"/>
-      <c r="H39" s="47"/>
-      <c r="I39" s="98"/>
-      <c r="L39" s="95"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="95"/>
+      <c r="E40" s="49"/>
+      <c r="F40" s="49"/>
+      <c r="G40" s="49"/>
+      <c r="H40" s="49"/>
+      <c r="I40" s="49"/>
+      <c r="J40" s="100"/>
+      <c r="M40" s="97"/>
+      <c r="N40" s="9"/>
+      <c r="O40" s="97"/>
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="C37:I37"/>
-    <mergeCell ref="C38:I38"/>
-    <mergeCell ref="L38:L39"/>
-    <mergeCell ref="N38:N39"/>
-    <mergeCell ref="C39:I39"/>
-    <mergeCell ref="L3:N4"/>
-    <mergeCell ref="E4:G6"/>
-    <mergeCell ref="L5:N23"/>
-    <mergeCell ref="E8:I8"/>
-    <mergeCell ref="C23:I23"/>
-    <mergeCell ref="F9:I9"/>
-    <mergeCell ref="C17:I17"/>
-    <mergeCell ref="C18:I18"/>
-    <mergeCell ref="A20:I20"/>
-    <mergeCell ref="C16:I16"/>
-    <mergeCell ref="C21:I21"/>
-    <mergeCell ref="C22:I22"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="L33:N33"/>
-    <mergeCell ref="C34:I34"/>
-    <mergeCell ref="L34:N35"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="C35:I36"/>
-    <mergeCell ref="L25:N26"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="L27:N31"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="C26:I27"/>
-    <mergeCell ref="C24:I25"/>
-    <mergeCell ref="C28:I28"/>
-    <mergeCell ref="C29:I29"/>
-    <mergeCell ref="C30:I30"/>
-    <mergeCell ref="A24:A25"/>
-    <mergeCell ref="B24:B25"/>
-    <mergeCell ref="C31:I31"/>
-    <mergeCell ref="A1:C2"/>
-    <mergeCell ref="A33:I33"/>
-    <mergeCell ref="E7:I7"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="B4:D6"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="F10:I10"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="C12:I12"/>
-    <mergeCell ref="A14:I14"/>
-    <mergeCell ref="C15:I15"/>
-    <mergeCell ref="D1:G1"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="E3:G3"/>
+    <mergeCell ref="D38:J38"/>
+    <mergeCell ref="D39:J39"/>
+    <mergeCell ref="M39:M40"/>
+    <mergeCell ref="O39:O40"/>
+    <mergeCell ref="D40:J40"/>
+    <mergeCell ref="M4:O5"/>
+    <mergeCell ref="F5:H7"/>
+    <mergeCell ref="M6:O24"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="D24:J24"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="D18:J18"/>
+    <mergeCell ref="D19:J19"/>
+    <mergeCell ref="B21:J21"/>
+    <mergeCell ref="D17:J17"/>
+    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="D23:J23"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="D35:J35"/>
+    <mergeCell ref="M35:O36"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:J37"/>
+    <mergeCell ref="M26:O27"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="M28:O32"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:J28"/>
+    <mergeCell ref="D25:J26"/>
+    <mergeCell ref="D29:J29"/>
+    <mergeCell ref="D30:J30"/>
+    <mergeCell ref="D31:J31"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D32:J32"/>
+    <mergeCell ref="B2:D3"/>
+    <mergeCell ref="B34:J34"/>
+    <mergeCell ref="F8:J8"/>
+    <mergeCell ref="B5:B7"/>
+    <mergeCell ref="C10:E10"/>
+    <mergeCell ref="C5:E7"/>
+    <mergeCell ref="C9:E9"/>
+    <mergeCell ref="G11:J11"/>
+    <mergeCell ref="C11:E11"/>
+    <mergeCell ref="D13:J13"/>
+    <mergeCell ref="B15:J15"/>
+    <mergeCell ref="D16:J16"/>
+    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="C4:E4"/>
+    <mergeCell ref="F4:H4"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>

--- a/example/sample.xlsx
+++ b/example/sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\ayebee\source\repos\Resumaker\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED04647F-934D-4FDD-8EB2-2D4FA4085662}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671749FE-0162-4160-83D4-B92A71AFD0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-150" yWindow="-150" windowWidth="38700" windowHeight="21180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-38540" yWindow="-140" windowWidth="38680" windowHeight="21880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="履歴書" sheetId="1" r:id="rId1"/>
@@ -124,10 +124,6 @@
     <phoneticPr fontId="13"/>
   </si>
   <si>
-    <t>{updated}</t>
-    <phoneticPr fontId="13"/>
-  </si>
-  <si>
     <t>{dob}</t>
     <phoneticPr fontId="13"/>
   </si>
@@ -411,6 +407,13 @@
   </si>
   <si>
     <t>{certificates[4].month}</t>
+  </si>
+  <si>
+    <t>{updated}現在</t>
+    <rPh sb="9" eb="11">
+      <t>ゲンザイ</t>
+    </rPh>
+    <phoneticPr fontId="13"/>
   </si>
 </sst>
 </file>
@@ -1783,7 +1786,7 @@
       <c r="C2" s="33"/>
       <c r="D2" s="33"/>
       <c r="E2" s="60" t="s">
-        <v>23</v>
+        <v>90</v>
       </c>
       <c r="F2" s="61"/>
       <c r="G2" s="61"/>
@@ -1852,7 +1855,7 @@
       <c r="H6" s="48"/>
       <c r="J6" s="14"/>
       <c r="M6" s="71" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N6" s="72"/>
       <c r="O6" s="73"/>
@@ -1876,12 +1879,12 @@
         <v>4</v>
       </c>
       <c r="C8" s="94" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D8" s="94"/>
       <c r="E8" s="95"/>
       <c r="F8" s="38" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G8" s="39"/>
       <c r="H8" s="39"/>
@@ -1896,7 +1899,7 @@
         <v>1</v>
       </c>
       <c r="C9" s="50" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D9" s="36"/>
       <c r="E9" s="36"/>
@@ -1916,7 +1919,7 @@
         <v>17</v>
       </c>
       <c r="C10" s="44" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D10" s="45"/>
       <c r="E10" s="46"/>
@@ -1924,7 +1927,7 @@
         <v>6</v>
       </c>
       <c r="G10" s="93" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H10" s="48"/>
       <c r="I10" s="48"/>
@@ -1938,7 +1941,7 @@
         <v>7</v>
       </c>
       <c r="C11" s="54" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D11" s="49"/>
       <c r="E11" s="49"/>
@@ -1946,7 +1949,7 @@
         <v>18</v>
       </c>
       <c r="G11" s="51" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H11" s="52"/>
       <c r="I11" s="52"/>
@@ -2012,13 +2015,13 @@
     </row>
     <row r="16" spans="2:15" ht="24.75" customHeight="1">
       <c r="B16" s="22" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D16" s="57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" s="58"/>
       <c r="F16" s="58"/>
@@ -2032,13 +2035,13 @@
     </row>
     <row r="17" spans="2:15" ht="24.75" customHeight="1">
       <c r="B17" s="22" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D17" s="57" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E17" s="58"/>
       <c r="F17" s="58"/>
@@ -2052,13 +2055,13 @@
     </row>
     <row r="18" spans="2:15" ht="24.75" customHeight="1">
       <c r="B18" s="22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D18" s="57" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E18" s="58"/>
       <c r="F18" s="58"/>
@@ -2072,13 +2075,13 @@
     </row>
     <row r="19" spans="2:15" ht="24.75" customHeight="1">
       <c r="B19" s="23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C19" s="24" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D19" s="84" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E19" s="85"/>
       <c r="F19" s="85"/>
@@ -2124,13 +2127,13 @@
     </row>
     <row r="22" spans="2:15" ht="24.75" customHeight="1">
       <c r="B22" s="22" t="s">
+        <v>40</v>
+      </c>
+      <c r="C22" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="D22" s="57" t="s">
         <v>42</v>
-      </c>
-      <c r="D22" s="57" t="s">
-        <v>43</v>
       </c>
       <c r="E22" s="58"/>
       <c r="F22" s="58"/>
@@ -2144,13 +2147,13 @@
     </row>
     <row r="23" spans="2:15" ht="24.75" customHeight="1">
       <c r="B23" s="22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D23" s="57" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E23" s="58"/>
       <c r="F23" s="58"/>
@@ -2164,13 +2167,13 @@
     </row>
     <row r="24" spans="2:15" ht="24.75" customHeight="1">
       <c r="B24" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D24" s="57" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E24" s="58"/>
       <c r="F24" s="58"/>
@@ -2184,13 +2187,13 @@
     </row>
     <row r="25" spans="2:15" ht="7.5" customHeight="1">
       <c r="B25" s="69" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="76" t="s">
         <v>50</v>
       </c>
-      <c r="C25" s="76" t="s">
+      <c r="D25" s="78" t="s">
         <v>51</v>
-      </c>
-      <c r="D25" s="78" t="s">
-        <v>52</v>
       </c>
       <c r="E25" s="79"/>
       <c r="F25" s="79"/>
@@ -2215,20 +2218,20 @@
       <c r="I26" s="82"/>
       <c r="J26" s="83"/>
       <c r="M26" s="64" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="N26" s="63"/>
       <c r="O26" s="65"/>
     </row>
     <row r="27" spans="2:15" ht="7.5" customHeight="1">
       <c r="B27" s="69" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="76" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="76" t="s">
+      <c r="D27" s="78" t="s">
         <v>54</v>
-      </c>
-      <c r="D27" s="78" t="s">
-        <v>55</v>
       </c>
       <c r="E27" s="79"/>
       <c r="F27" s="79"/>
@@ -2251,20 +2254,20 @@
       <c r="I28" s="82"/>
       <c r="J28" s="83"/>
       <c r="M28" s="71" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="N28" s="72"/>
       <c r="O28" s="73"/>
     </row>
     <row r="29" spans="2:15" ht="24.75" customHeight="1">
       <c r="B29" s="22" t="s">
+        <v>55</v>
+      </c>
+      <c r="C29" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C29" s="7" t="s">
+      <c r="D29" s="57" t="s">
         <v>57</v>
-      </c>
-      <c r="D29" s="57" t="s">
-        <v>58</v>
       </c>
       <c r="E29" s="58"/>
       <c r="F29" s="58"/>
@@ -2278,13 +2281,13 @@
     </row>
     <row r="30" spans="2:15" ht="24.75" customHeight="1">
       <c r="B30" s="22" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D30" s="57" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E30" s="58"/>
       <c r="F30" s="58"/>
@@ -2298,13 +2301,13 @@
     </row>
     <row r="31" spans="2:15" ht="24.75" customHeight="1">
       <c r="B31" s="22" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D31" s="57" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E31" s="58"/>
       <c r="F31" s="58"/>
@@ -2318,13 +2321,13 @@
     </row>
     <row r="32" spans="2:15" ht="24.75" customHeight="1">
       <c r="B32" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C32" s="24" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D32" s="84" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E32" s="85"/>
       <c r="F32" s="85"/>
@@ -2367,13 +2370,13 @@
     </row>
     <row r="35" spans="2:15" ht="24.75" customHeight="1">
       <c r="B35" s="22" t="s">
+        <v>67</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="D35" s="57" t="s">
         <v>68</v>
-      </c>
-      <c r="C35" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="D35" s="57" t="s">
-        <v>69</v>
       </c>
       <c r="E35" s="58"/>
       <c r="F35" s="58"/>
@@ -2382,20 +2385,20 @@
       <c r="I35" s="58"/>
       <c r="J35" s="59"/>
       <c r="M35" s="87" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="N35" s="72"/>
       <c r="O35" s="73"/>
     </row>
     <row r="36" spans="2:15" ht="17.25" customHeight="1">
       <c r="B36" s="69" t="s">
+        <v>69</v>
+      </c>
+      <c r="C36" s="76" t="s">
+        <v>86</v>
+      </c>
+      <c r="D36" s="78" t="s">
         <v>70</v>
-      </c>
-      <c r="C36" s="76" t="s">
-        <v>87</v>
-      </c>
-      <c r="D36" s="78" t="s">
-        <v>71</v>
       </c>
       <c r="E36" s="79"/>
       <c r="F36" s="79"/>
@@ -2423,13 +2426,13 @@
     </row>
     <row r="38" spans="2:15" ht="24.75" customHeight="1">
       <c r="B38" s="26" t="s">
+        <v>71</v>
+      </c>
+      <c r="C38" s="27" t="s">
+        <v>87</v>
+      </c>
+      <c r="D38" s="81" t="s">
         <v>72</v>
-      </c>
-      <c r="C38" s="27" t="s">
-        <v>88</v>
-      </c>
-      <c r="D38" s="81" t="s">
-        <v>73</v>
       </c>
       <c r="E38" s="67"/>
       <c r="F38" s="67"/>
@@ -2447,13 +2450,13 @@
     </row>
     <row r="39" spans="2:15" ht="24.75" customHeight="1">
       <c r="B39" s="26" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C39" s="27" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D39" s="81" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E39" s="67"/>
       <c r="F39" s="67"/>
@@ -2462,22 +2465,22 @@
       <c r="I39" s="67"/>
       <c r="J39" s="68"/>
       <c r="M39" s="96" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N39" s="9"/>
       <c r="O39" s="98" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="40" spans="2:15" ht="24.75" customHeight="1">
       <c r="B40" s="31" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C40" s="32" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D40" s="99" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E40" s="49"/>
       <c r="F40" s="49"/>

--- a/example/sample.xlsx
+++ b/example/sample.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\ayebee\source\repos\Resumaker\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{671749FE-0162-4160-83D4-B92A71AFD0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{848CFACC-6BC2-43A3-A5CF-8F6BB62B6E79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38540" yWindow="-140" windowWidth="38680" windowHeight="21880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-150" yWindow="-150" windowWidth="38700" windowHeight="21180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="履歴書" sheetId="1" r:id="rId1"/>
@@ -1166,7 +1166,7 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="101">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1192,9 +1192,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="178" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1266,21 +1263,162 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="8" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="8" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1292,9 +1430,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1311,24 +1446,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="20" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1338,15 +1461,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="179" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1356,119 +1470,38 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="8" fillId="0" borderId="47" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="45" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="8" fillId="0" borderId="44" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1780,183 +1813,183 @@
   <sheetData>
     <row r="1" spans="2:15" ht="3.75" customHeight="1"/>
     <row r="2" spans="2:15" ht="30" customHeight="1">
-      <c r="B2" s="33" t="s">
+      <c r="B2" s="82" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="33"/>
-      <c r="D2" s="33"/>
-      <c r="E2" s="60" t="s">
+      <c r="C2" s="82"/>
+      <c r="D2" s="82"/>
+      <c r="E2" s="98" t="s">
         <v>90</v>
       </c>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
+      <c r="F2" s="99"/>
+      <c r="G2" s="99"/>
+      <c r="H2" s="99"/>
       <c r="I2" s="2"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
     </row>
     <row r="3" spans="2:15" ht="7.5" customHeight="1">
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
+      <c r="B3" s="83"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
       <c r="F3" s="3"/>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
     </row>
     <row r="4" spans="2:15" ht="17.25" customHeight="1">
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="50" t="s">
+      <c r="C4" s="93" t="s">
         <v>21</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" s="36"/>
-      <c r="F4" s="62" t="s">
+      <c r="D4" s="68"/>
+      <c r="E4" s="68"/>
+      <c r="F4" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
-      <c r="I4" s="12"/>
-      <c r="J4" s="13"/>
-      <c r="M4" s="64" t="s">
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
+      <c r="I4" s="11"/>
+      <c r="J4" s="12"/>
+      <c r="M4" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="N4" s="63"/>
-      <c r="O4" s="65"/>
+      <c r="N4" s="43"/>
+      <c r="O4" s="44"/>
     </row>
     <row r="5" spans="2:15" ht="7.5" customHeight="1">
-      <c r="B5" s="41" t="s">
+      <c r="B5" s="87" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="92" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="88" t="s">
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="46" t="s">
         <v>22</v>
       </c>
-      <c r="G5" s="48"/>
-      <c r="H5" s="48"/>
-      <c r="J5" s="14"/>
-      <c r="M5" s="66"/>
-      <c r="N5" s="67"/>
-      <c r="O5" s="68"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="J5" s="13"/>
+      <c r="M5" s="45"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="35"/>
     </row>
     <row r="6" spans="2:15" ht="16.5" customHeight="1">
-      <c r="B6" s="42"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="89"/>
-      <c r="G6" s="48"/>
-      <c r="H6" s="48"/>
-      <c r="J6" s="14"/>
-      <c r="M6" s="71" t="s">
+      <c r="B6" s="53"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="48"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="J6" s="13"/>
+      <c r="M6" s="50" t="s">
         <v>77</v>
       </c>
-      <c r="N6" s="72"/>
-      <c r="O6" s="73"/>
+      <c r="N6" s="101"/>
+      <c r="O6" s="102"/>
     </row>
     <row r="7" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B7" s="43"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="90"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="16"/>
-      <c r="M7" s="42"/>
-      <c r="N7" s="48"/>
-      <c r="O7" s="74"/>
+      <c r="B7" s="88"/>
+      <c r="C7" s="40"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="40"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="40"/>
+      <c r="H7" s="40"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="15"/>
+      <c r="M7" s="103"/>
+      <c r="N7" s="104"/>
+      <c r="O7" s="105"/>
     </row>
     <row r="8" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B8" s="19" t="s">
+      <c r="B8" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="94" t="s">
+      <c r="C8" s="70" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="94"/>
-      <c r="E8" s="95"/>
-      <c r="F8" s="38" t="s">
+      <c r="D8" s="70"/>
+      <c r="E8" s="71"/>
+      <c r="F8" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="G8" s="39"/>
-      <c r="H8" s="39"/>
-      <c r="I8" s="39"/>
-      <c r="J8" s="40"/>
-      <c r="M8" s="42"/>
-      <c r="N8" s="48"/>
-      <c r="O8" s="74"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="85"/>
+      <c r="J8" s="86"/>
+      <c r="M8" s="103"/>
+      <c r="N8" s="104"/>
+      <c r="O8" s="105"/>
     </row>
     <row r="9" spans="2:15" ht="17.25" customHeight="1">
-      <c r="B9" s="11" t="s">
+      <c r="B9" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="C9" s="50" t="s">
+      <c r="C9" s="93" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="64" t="s">
+      <c r="D9" s="68"/>
+      <c r="E9" s="68"/>
+      <c r="F9" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="G9" s="91"/>
-      <c r="H9" s="91"/>
-      <c r="I9" s="91"/>
-      <c r="J9" s="92"/>
-      <c r="M9" s="42"/>
-      <c r="N9" s="48"/>
-      <c r="O9" s="74"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="59"/>
+      <c r="M9" s="103"/>
+      <c r="N9" s="104"/>
+      <c r="O9" s="105"/>
     </row>
     <row r="10" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="44" t="s">
+      <c r="C10" s="89" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="45"/>
-      <c r="E10" s="46"/>
-      <c r="F10" s="28" t="s">
+      <c r="D10" s="90"/>
+      <c r="E10" s="91"/>
+      <c r="F10" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="G10" s="93" t="s">
+      <c r="G10" s="63" t="s">
         <v>84</v>
       </c>
-      <c r="H10" s="48"/>
-      <c r="I10" s="48"/>
-      <c r="J10" s="74"/>
-      <c r="M10" s="42"/>
-      <c r="N10" s="48"/>
-      <c r="O10" s="74"/>
+      <c r="H10" s="47"/>
+      <c r="I10" s="47"/>
+      <c r="J10" s="54"/>
+      <c r="M10" s="103"/>
+      <c r="N10" s="104"/>
+      <c r="O10" s="105"/>
     </row>
     <row r="11" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B11" s="17" t="s">
+      <c r="B11" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="C11" s="54" t="s">
+      <c r="C11" s="95" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="49"/>
-      <c r="E11" s="49"/>
-      <c r="F11" s="30" t="s">
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="G11" s="51" t="s">
+      <c r="G11" s="94" t="s">
         <v>83</v>
       </c>
-      <c r="H11" s="52"/>
-      <c r="I11" s="52"/>
-      <c r="J11" s="53"/>
-      <c r="M11" s="42"/>
-      <c r="N11" s="48"/>
-      <c r="O11" s="74"/>
+      <c r="H11" s="56"/>
+      <c r="I11" s="56"/>
+      <c r="J11" s="57"/>
+      <c r="M11" s="103"/>
+      <c r="N11" s="104"/>
+      <c r="O11" s="105"/>
     </row>
     <row r="12" spans="2:15" ht="7.5" customHeight="1">
       <c r="B12" s="5"/>
@@ -1968,130 +2001,130 @@
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
       <c r="J12" s="6"/>
-      <c r="M12" s="42"/>
-      <c r="N12" s="48"/>
-      <c r="O12" s="74"/>
+      <c r="M12" s="103"/>
+      <c r="N12" s="104"/>
+      <c r="O12" s="105"/>
     </row>
     <row r="13" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="38" t="s">
+      <c r="D13" s="84" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="55"/>
-      <c r="F13" s="55"/>
-      <c r="G13" s="55"/>
-      <c r="H13" s="55"/>
-      <c r="I13" s="55"/>
-      <c r="J13" s="56"/>
-      <c r="M13" s="42"/>
-      <c r="N13" s="48"/>
-      <c r="O13" s="74"/>
+      <c r="E13" s="96"/>
+      <c r="F13" s="96"/>
+      <c r="G13" s="96"/>
+      <c r="H13" s="96"/>
+      <c r="I13" s="96"/>
+      <c r="J13" s="97"/>
+      <c r="M13" s="103"/>
+      <c r="N13" s="104"/>
+      <c r="O13" s="105"/>
     </row>
     <row r="14" spans="2:15" ht="7.5" customHeight="1">
-      <c r="M14" s="42"/>
-      <c r="N14" s="48"/>
-      <c r="O14" s="74"/>
+      <c r="M14" s="103"/>
+      <c r="N14" s="104"/>
+      <c r="O14" s="105"/>
     </row>
     <row r="15" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B15" s="35" t="s">
+      <c r="B15" s="67" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="36"/>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" s="36"/>
-      <c r="G15" s="36"/>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" s="37"/>
-      <c r="M15" s="42"/>
-      <c r="N15" s="48"/>
-      <c r="O15" s="74"/>
+      <c r="C15" s="68"/>
+      <c r="D15" s="68"/>
+      <c r="E15" s="68"/>
+      <c r="F15" s="68"/>
+      <c r="G15" s="68"/>
+      <c r="H15" s="68"/>
+      <c r="I15" s="68"/>
+      <c r="J15" s="69"/>
+      <c r="M15" s="103"/>
+      <c r="N15" s="104"/>
+      <c r="O15" s="105"/>
     </row>
     <row r="16" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B16" s="22" t="s">
+      <c r="B16" s="21" t="s">
         <v>28</v>
       </c>
       <c r="C16" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="D16" s="57" t="s">
+      <c r="D16" s="60" t="s">
         <v>32</v>
       </c>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
-      <c r="J16" s="59"/>
-      <c r="M16" s="42"/>
-      <c r="N16" s="48"/>
-      <c r="O16" s="74"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="61"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="62"/>
+      <c r="M16" s="103"/>
+      <c r="N16" s="104"/>
+      <c r="O16" s="105"/>
     </row>
     <row r="17" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B17" s="22" t="s">
+      <c r="B17" s="21" t="s">
         <v>29</v>
       </c>
       <c r="C17" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D17" s="57" t="s">
+      <c r="D17" s="60" t="s">
         <v>37</v>
       </c>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
-      <c r="J17" s="59"/>
-      <c r="M17" s="42"/>
-      <c r="N17" s="48"/>
-      <c r="O17" s="74"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="61"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="62"/>
+      <c r="M17" s="103"/>
+      <c r="N17" s="104"/>
+      <c r="O17" s="105"/>
     </row>
     <row r="18" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="21" t="s">
         <v>33</v>
       </c>
       <c r="C18" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D18" s="57" t="s">
+      <c r="D18" s="60" t="s">
         <v>38</v>
       </c>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="58"/>
-      <c r="J18" s="59"/>
-      <c r="M18" s="42"/>
-      <c r="N18" s="48"/>
-      <c r="O18" s="74"/>
+      <c r="E18" s="61"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
+      <c r="H18" s="61"/>
+      <c r="I18" s="61"/>
+      <c r="J18" s="62"/>
+      <c r="M18" s="103"/>
+      <c r="N18" s="104"/>
+      <c r="O18" s="105"/>
     </row>
     <row r="19" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="22" t="s">
         <v>34</v>
       </c>
-      <c r="C19" s="24" t="s">
+      <c r="C19" s="23" t="s">
         <v>36</v>
       </c>
-      <c r="D19" s="84" t="s">
+      <c r="D19" s="64" t="s">
         <v>39</v>
       </c>
-      <c r="E19" s="85"/>
-      <c r="F19" s="85"/>
-      <c r="G19" s="85"/>
-      <c r="H19" s="85"/>
-      <c r="I19" s="85"/>
-      <c r="J19" s="86"/>
-      <c r="M19" s="42"/>
-      <c r="N19" s="48"/>
-      <c r="O19" s="74"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="66"/>
+      <c r="M19" s="103"/>
+      <c r="N19" s="104"/>
+      <c r="O19" s="105"/>
     </row>
     <row r="20" spans="2:15" ht="7.5" customHeight="1">
       <c r="B20" s="3"/>
@@ -2105,431 +2138,394 @@
       <c r="J20" s="3"/>
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
-      <c r="M20" s="42"/>
-      <c r="N20" s="48"/>
-      <c r="O20" s="74"/>
+      <c r="M20" s="32"/>
+      <c r="O20" s="13"/>
     </row>
     <row r="21" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B21" s="35" t="s">
+      <c r="B21" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="C21" s="36"/>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="37"/>
-      <c r="M21" s="42"/>
-      <c r="N21" s="48"/>
-      <c r="O21" s="74"/>
+      <c r="C21" s="68"/>
+      <c r="D21" s="68"/>
+      <c r="E21" s="68"/>
+      <c r="F21" s="68"/>
+      <c r="G21" s="68"/>
+      <c r="H21" s="68"/>
+      <c r="I21" s="68"/>
+      <c r="J21" s="69"/>
+      <c r="M21" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="N21" s="58"/>
+      <c r="O21" s="59"/>
     </row>
     <row r="22" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B22" s="22" t="s">
+      <c r="B22" s="21" t="s">
         <v>40</v>
       </c>
       <c r="C22" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D22" s="57" t="s">
+      <c r="D22" s="60" t="s">
         <v>42</v>
       </c>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
-      <c r="J22" s="59"/>
-      <c r="M22" s="42"/>
-      <c r="N22" s="48"/>
-      <c r="O22" s="74"/>
+      <c r="E22" s="61"/>
+      <c r="F22" s="61"/>
+      <c r="G22" s="61"/>
+      <c r="H22" s="61"/>
+      <c r="I22" s="61"/>
+      <c r="J22" s="62"/>
+      <c r="M22" s="107" t="s">
+        <v>82</v>
+      </c>
+      <c r="N22" s="108"/>
+      <c r="O22" s="109"/>
     </row>
     <row r="23" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B23" s="22" t="s">
+      <c r="B23" s="21" t="s">
         <v>43</v>
       </c>
       <c r="C23" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="D23" s="57" t="s">
+      <c r="D23" s="60" t="s">
         <v>47</v>
       </c>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="58"/>
-      <c r="J23" s="59"/>
-      <c r="M23" s="42"/>
-      <c r="N23" s="48"/>
-      <c r="O23" s="74"/>
+      <c r="E23" s="61"/>
+      <c r="F23" s="61"/>
+      <c r="G23" s="61"/>
+      <c r="H23" s="61"/>
+      <c r="I23" s="61"/>
+      <c r="J23" s="62"/>
+      <c r="M23" s="103"/>
+      <c r="N23" s="104"/>
+      <c r="O23" s="105"/>
     </row>
     <row r="24" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B24" s="22" t="s">
+      <c r="B24" s="21" t="s">
         <v>44</v>
       </c>
       <c r="C24" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D24" s="57" t="s">
+      <c r="D24" s="60" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
-      <c r="J24" s="59"/>
-      <c r="M24" s="75"/>
-      <c r="N24" s="52"/>
-      <c r="O24" s="53"/>
+      <c r="E24" s="61"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="61"/>
+      <c r="H24" s="61"/>
+      <c r="I24" s="61"/>
+      <c r="J24" s="62"/>
+      <c r="M24" s="103"/>
+      <c r="N24" s="104"/>
+      <c r="O24" s="105"/>
     </row>
     <row r="25" spans="2:15" ht="7.5" customHeight="1">
-      <c r="B25" s="69" t="s">
+      <c r="B25" s="73" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="76" t="s">
+      <c r="C25" s="75" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="78" t="s">
+      <c r="D25" s="77" t="s">
         <v>51</v>
       </c>
-      <c r="E25" s="79"/>
-      <c r="F25" s="79"/>
-      <c r="G25" s="79"/>
-      <c r="H25" s="79"/>
-      <c r="I25" s="79"/>
-      <c r="J25" s="80"/>
+      <c r="E25" s="78"/>
+      <c r="F25" s="78"/>
+      <c r="G25" s="78"/>
+      <c r="H25" s="78"/>
+      <c r="I25" s="78"/>
+      <c r="J25" s="79"/>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
-      <c r="M25" s="8"/>
-      <c r="N25" s="8"/>
-      <c r="O25" s="8"/>
+      <c r="M25" s="103"/>
+      <c r="N25" s="104"/>
+      <c r="O25" s="105"/>
     </row>
     <row r="26" spans="2:15" ht="17.25" customHeight="1">
-      <c r="B26" s="70"/>
-      <c r="C26" s="77"/>
-      <c r="D26" s="81"/>
-      <c r="E26" s="82"/>
-      <c r="F26" s="82"/>
-      <c r="G26" s="82"/>
-      <c r="H26" s="82"/>
-      <c r="I26" s="82"/>
-      <c r="J26" s="83"/>
-      <c r="M26" s="64" t="s">
-        <v>81</v>
-      </c>
-      <c r="N26" s="63"/>
-      <c r="O26" s="65"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="76"/>
+      <c r="D26" s="33"/>
+      <c r="E26" s="80"/>
+      <c r="F26" s="80"/>
+      <c r="G26" s="80"/>
+      <c r="H26" s="80"/>
+      <c r="I26" s="80"/>
+      <c r="J26" s="81"/>
+      <c r="M26" s="103"/>
+      <c r="N26" s="104"/>
+      <c r="O26" s="105"/>
     </row>
     <row r="27" spans="2:15" ht="7.5" customHeight="1">
-      <c r="B27" s="69" t="s">
+      <c r="B27" s="73" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="76" t="s">
+      <c r="C27" s="75" t="s">
         <v>53</v>
       </c>
-      <c r="D27" s="78" t="s">
+      <c r="D27" s="77" t="s">
         <v>54</v>
       </c>
-      <c r="E27" s="79"/>
-      <c r="F27" s="79"/>
-      <c r="G27" s="79"/>
-      <c r="H27" s="79"/>
-      <c r="I27" s="79"/>
-      <c r="J27" s="80"/>
-      <c r="M27" s="66"/>
-      <c r="N27" s="67"/>
-      <c r="O27" s="68"/>
+      <c r="E27" s="78"/>
+      <c r="F27" s="78"/>
+      <c r="G27" s="78"/>
+      <c r="H27" s="78"/>
+      <c r="I27" s="78"/>
+      <c r="J27" s="79"/>
+      <c r="M27" s="103"/>
+      <c r="N27" s="104"/>
+      <c r="O27" s="105"/>
     </row>
     <row r="28" spans="2:15" ht="17.25" customHeight="1">
-      <c r="B28" s="70"/>
-      <c r="C28" s="77"/>
-      <c r="D28" s="81"/>
-      <c r="E28" s="82"/>
-      <c r="F28" s="82"/>
-      <c r="G28" s="82"/>
-      <c r="H28" s="82"/>
-      <c r="I28" s="82"/>
-      <c r="J28" s="83"/>
-      <c r="M28" s="71" t="s">
-        <v>82</v>
-      </c>
-      <c r="N28" s="72"/>
-      <c r="O28" s="73"/>
+      <c r="B28" s="74"/>
+      <c r="C28" s="76"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="80"/>
+      <c r="F28" s="80"/>
+      <c r="G28" s="80"/>
+      <c r="H28" s="80"/>
+      <c r="I28" s="80"/>
+      <c r="J28" s="81"/>
+      <c r="M28" s="103"/>
+      <c r="N28" s="104"/>
+      <c r="O28" s="105"/>
     </row>
     <row r="29" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B29" s="22" t="s">
+      <c r="B29" s="21" t="s">
         <v>55</v>
       </c>
       <c r="C29" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D29" s="57" t="s">
+      <c r="D29" s="60" t="s">
         <v>57</v>
       </c>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
-      <c r="J29" s="59"/>
-      <c r="M29" s="42"/>
-      <c r="N29" s="48"/>
-      <c r="O29" s="74"/>
+      <c r="E29" s="61"/>
+      <c r="F29" s="61"/>
+      <c r="G29" s="61"/>
+      <c r="H29" s="61"/>
+      <c r="I29" s="61"/>
+      <c r="J29" s="62"/>
+      <c r="M29" s="103"/>
+      <c r="N29" s="104"/>
+      <c r="O29" s="105"/>
     </row>
     <row r="30" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B30" s="22" t="s">
+      <c r="B30" s="21" t="s">
         <v>58</v>
       </c>
       <c r="C30" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="D30" s="57" t="s">
+      <c r="D30" s="60" t="s">
         <v>64</v>
       </c>
-      <c r="E30" s="58"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="58"/>
-      <c r="J30" s="59"/>
-      <c r="M30" s="42"/>
-      <c r="N30" s="48"/>
-      <c r="O30" s="74"/>
+      <c r="E30" s="61"/>
+      <c r="F30" s="61"/>
+      <c r="G30" s="61"/>
+      <c r="H30" s="61"/>
+      <c r="I30" s="61"/>
+      <c r="J30" s="62"/>
+      <c r="M30" s="103"/>
+      <c r="N30" s="104"/>
+      <c r="O30" s="105"/>
     </row>
     <row r="31" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="21" t="s">
         <v>59</v>
       </c>
       <c r="C31" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="D31" s="57" t="s">
+      <c r="D31" s="60" t="s">
         <v>65</v>
       </c>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
-      <c r="J31" s="59"/>
-      <c r="M31" s="42"/>
-      <c r="N31" s="48"/>
-      <c r="O31" s="74"/>
+      <c r="E31" s="61"/>
+      <c r="F31" s="61"/>
+      <c r="G31" s="61"/>
+      <c r="H31" s="61"/>
+      <c r="I31" s="61"/>
+      <c r="J31" s="62"/>
+      <c r="M31" s="103"/>
+      <c r="N31" s="104"/>
+      <c r="O31" s="105"/>
     </row>
     <row r="32" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B32" s="23" t="s">
+      <c r="B32" s="22" t="s">
         <v>60</v>
       </c>
-      <c r="C32" s="24" t="s">
+      <c r="C32" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="D32" s="84" t="s">
+      <c r="D32" s="64" t="s">
         <v>66</v>
       </c>
-      <c r="E32" s="85"/>
-      <c r="F32" s="85"/>
-      <c r="G32" s="85"/>
-      <c r="H32" s="85"/>
-      <c r="I32" s="85"/>
-      <c r="J32" s="86"/>
-      <c r="M32" s="75"/>
-      <c r="N32" s="52"/>
-      <c r="O32" s="53"/>
+      <c r="E32" s="65"/>
+      <c r="F32" s="65"/>
+      <c r="G32" s="65"/>
+      <c r="H32" s="65"/>
+      <c r="I32" s="65"/>
+      <c r="J32" s="66"/>
+      <c r="M32" s="110"/>
+      <c r="N32" s="106"/>
+      <c r="O32" s="111"/>
     </row>
     <row r="33" spans="2:15" ht="7.5" customHeight="1">
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
-      <c r="J33" s="18"/>
+      <c r="B33" s="17"/>
+      <c r="C33" s="17"/>
+      <c r="D33" s="17"/>
+      <c r="E33" s="17"/>
+      <c r="F33" s="17"/>
+      <c r="G33" s="17"/>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17"/>
+      <c r="J33" s="17"/>
     </row>
     <row r="34" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B34" s="35" t="s">
+      <c r="B34" s="67" t="s">
         <v>16</v>
       </c>
-      <c r="C34" s="36"/>
-      <c r="D34" s="36"/>
-      <c r="E34" s="36"/>
-      <c r="F34" s="36"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="36"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="37"/>
-      <c r="M34" s="35" t="s">
+      <c r="C34" s="68"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="68"/>
+      <c r="G34" s="68"/>
+      <c r="H34" s="68"/>
+      <c r="I34" s="68"/>
+      <c r="J34" s="69"/>
+      <c r="M34" s="67" t="s">
         <v>13</v>
       </c>
-      <c r="N34" s="36"/>
-      <c r="O34" s="37"/>
+      <c r="N34" s="68"/>
+      <c r="O34" s="69"/>
     </row>
     <row r="35" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="21" t="s">
         <v>67</v>
       </c>
       <c r="C35" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="D35" s="57" t="s">
+      <c r="D35" s="60" t="s">
         <v>68</v>
       </c>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
-      <c r="J35" s="59"/>
-      <c r="M35" s="87" t="s">
+      <c r="E35" s="61"/>
+      <c r="F35" s="61"/>
+      <c r="G35" s="61"/>
+      <c r="H35" s="61"/>
+      <c r="I35" s="61"/>
+      <c r="J35" s="62"/>
+      <c r="M35" s="72" t="s">
         <v>78</v>
       </c>
-      <c r="N35" s="72"/>
-      <c r="O35" s="73"/>
+      <c r="N35" s="51"/>
+      <c r="O35" s="52"/>
     </row>
     <row r="36" spans="2:15" ht="17.25" customHeight="1">
-      <c r="B36" s="69" t="s">
+      <c r="B36" s="73" t="s">
         <v>69</v>
       </c>
-      <c r="C36" s="76" t="s">
+      <c r="C36" s="75" t="s">
         <v>86</v>
       </c>
-      <c r="D36" s="78" t="s">
+      <c r="D36" s="77" t="s">
         <v>70</v>
       </c>
-      <c r="E36" s="79"/>
-      <c r="F36" s="79"/>
-      <c r="G36" s="79"/>
-      <c r="H36" s="79"/>
-      <c r="I36" s="79"/>
-      <c r="J36" s="80"/>
-      <c r="M36" s="75"/>
-      <c r="N36" s="52"/>
-      <c r="O36" s="53"/>
+      <c r="E36" s="78"/>
+      <c r="F36" s="78"/>
+      <c r="G36" s="78"/>
+      <c r="H36" s="78"/>
+      <c r="I36" s="78"/>
+      <c r="J36" s="79"/>
+      <c r="M36" s="55"/>
+      <c r="N36" s="56"/>
+      <c r="O36" s="57"/>
     </row>
     <row r="37" spans="2:15" ht="7.5" customHeight="1">
-      <c r="B37" s="70"/>
-      <c r="C37" s="77"/>
-      <c r="D37" s="81"/>
-      <c r="E37" s="82"/>
-      <c r="F37" s="82"/>
-      <c r="G37" s="82"/>
-      <c r="H37" s="82"/>
-      <c r="I37" s="82"/>
-      <c r="J37" s="83"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-      <c r="O37" s="10"/>
+      <c r="B37" s="74"/>
+      <c r="C37" s="76"/>
+      <c r="D37" s="33"/>
+      <c r="E37" s="80"/>
+      <c r="F37" s="80"/>
+      <c r="G37" s="80"/>
+      <c r="H37" s="80"/>
+      <c r="I37" s="80"/>
+      <c r="J37" s="81"/>
+      <c r="M37" s="8"/>
+      <c r="N37" s="8"/>
+      <c r="O37" s="9"/>
     </row>
     <row r="38" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B38" s="26" t="s">
+      <c r="B38" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="C38" s="27" t="s">
+      <c r="C38" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="D38" s="81" t="s">
+      <c r="D38" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="E38" s="67"/>
-      <c r="F38" s="67"/>
-      <c r="G38" s="67"/>
-      <c r="H38" s="67"/>
-      <c r="I38" s="67"/>
-      <c r="J38" s="68"/>
-      <c r="M38" s="25" t="s">
+      <c r="E38" s="34"/>
+      <c r="F38" s="34"/>
+      <c r="G38" s="34"/>
+      <c r="H38" s="34"/>
+      <c r="I38" s="34"/>
+      <c r="J38" s="35"/>
+      <c r="M38" s="24" t="s">
         <v>14</v>
       </c>
       <c r="N38" s="4"/>
-      <c r="O38" s="25" t="s">
+      <c r="O38" s="24" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="39" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B39" s="26" t="s">
+      <c r="B39" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C39" s="27" t="s">
+      <c r="C39" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="D39" s="81" t="s">
+      <c r="D39" s="33" t="s">
         <v>75</v>
       </c>
-      <c r="E39" s="67"/>
-      <c r="F39" s="67"/>
-      <c r="G39" s="67"/>
-      <c r="H39" s="67"/>
-      <c r="I39" s="67"/>
-      <c r="J39" s="68"/>
-      <c r="M39" s="96" t="s">
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="34"/>
+      <c r="J39" s="35"/>
+      <c r="M39" s="36" t="s">
         <v>79</v>
       </c>
-      <c r="N39" s="9"/>
-      <c r="O39" s="98" t="s">
+      <c r="N39" s="8"/>
+      <c r="O39" s="38" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="40" spans="2:15" ht="24.75" customHeight="1">
-      <c r="B40" s="31" t="s">
+      <c r="B40" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="C40" s="32" t="s">
+      <c r="C40" s="31" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="99" t="s">
+      <c r="D40" s="39" t="s">
         <v>76</v>
       </c>
-      <c r="E40" s="49"/>
-      <c r="F40" s="49"/>
-      <c r="G40" s="49"/>
-      <c r="H40" s="49"/>
-      <c r="I40" s="49"/>
-      <c r="J40" s="100"/>
-      <c r="M40" s="97"/>
-      <c r="N40" s="9"/>
-      <c r="O40" s="97"/>
+      <c r="E40" s="40"/>
+      <c r="F40" s="40"/>
+      <c r="G40" s="40"/>
+      <c r="H40" s="40"/>
+      <c r="I40" s="40"/>
+      <c r="J40" s="41"/>
+      <c r="M40" s="37"/>
+      <c r="N40" s="8"/>
+      <c r="O40" s="37"/>
     </row>
   </sheetData>
   <mergeCells count="51">
-    <mergeCell ref="D38:J38"/>
-    <mergeCell ref="D39:J39"/>
-    <mergeCell ref="M39:M40"/>
-    <mergeCell ref="O39:O40"/>
-    <mergeCell ref="D40:J40"/>
-    <mergeCell ref="M4:O5"/>
-    <mergeCell ref="F5:H7"/>
-    <mergeCell ref="M6:O24"/>
-    <mergeCell ref="F9:J9"/>
-    <mergeCell ref="D24:J24"/>
-    <mergeCell ref="G10:J10"/>
-    <mergeCell ref="D18:J18"/>
-    <mergeCell ref="D19:J19"/>
-    <mergeCell ref="B21:J21"/>
-    <mergeCell ref="D17:J17"/>
-    <mergeCell ref="D22:J22"/>
-    <mergeCell ref="D23:J23"/>
-    <mergeCell ref="C8:E8"/>
-    <mergeCell ref="M34:O34"/>
-    <mergeCell ref="D35:J35"/>
-    <mergeCell ref="M35:O36"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="D36:J37"/>
-    <mergeCell ref="M26:O27"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="M28:O32"/>
-    <mergeCell ref="C27:C28"/>
-    <mergeCell ref="D27:J28"/>
-    <mergeCell ref="D25:J26"/>
-    <mergeCell ref="D29:J29"/>
-    <mergeCell ref="D30:J30"/>
-    <mergeCell ref="D31:J31"/>
-    <mergeCell ref="B25:B26"/>
-    <mergeCell ref="C25:C26"/>
-    <mergeCell ref="D32:J32"/>
     <mergeCell ref="B2:D3"/>
     <mergeCell ref="B34:J34"/>
     <mergeCell ref="F8:J8"/>
@@ -2545,6 +2541,42 @@
     <mergeCell ref="E2:H2"/>
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="F4:H4"/>
+    <mergeCell ref="B27:B28"/>
+    <mergeCell ref="C27:C28"/>
+    <mergeCell ref="D27:J28"/>
+    <mergeCell ref="D25:J26"/>
+    <mergeCell ref="D29:J29"/>
+    <mergeCell ref="D30:J30"/>
+    <mergeCell ref="D31:J31"/>
+    <mergeCell ref="B25:B26"/>
+    <mergeCell ref="C25:C26"/>
+    <mergeCell ref="D32:J32"/>
+    <mergeCell ref="M22:O32"/>
+    <mergeCell ref="M34:O34"/>
+    <mergeCell ref="D35:J35"/>
+    <mergeCell ref="M35:O36"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="D36:J37"/>
+    <mergeCell ref="M4:O5"/>
+    <mergeCell ref="F5:H7"/>
+    <mergeCell ref="F9:J9"/>
+    <mergeCell ref="D24:J24"/>
+    <mergeCell ref="G10:J10"/>
+    <mergeCell ref="D18:J18"/>
+    <mergeCell ref="D19:J19"/>
+    <mergeCell ref="B21:J21"/>
+    <mergeCell ref="D17:J17"/>
+    <mergeCell ref="D22:J22"/>
+    <mergeCell ref="D23:J23"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="M6:O19"/>
+    <mergeCell ref="M21:O21"/>
+    <mergeCell ref="D38:J38"/>
+    <mergeCell ref="D39:J39"/>
+    <mergeCell ref="M39:M40"/>
+    <mergeCell ref="O39:O40"/>
+    <mergeCell ref="D40:J40"/>
   </mergeCells>
   <phoneticPr fontId="13"/>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
